--- a/Tools/Luban/MiniTemplate/Data/__tables__.xlsx
+++ b/Tools/Luban/MiniTemplate/Data/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -115,16 +115,28 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbFightBuffNew</t>
-  </si>
-  <si>
-    <t>FightBuffNew</t>
-  </si>
-  <si>
-    <t>fightBuffNewJsonInfo.xlsx</t>
+    <t>TbFightBuffNewJsonInfo</t>
+  </si>
+  <si>
+    <t>FightBuffNewJsonInfo</t>
+  </si>
+  <si>
+    <t>2_战斗buff.xlsx</t>
   </si>
   <si>
     <t>战斗buff</t>
+  </si>
+  <si>
+    <t>TbHeroAtkJsonInfo</t>
+  </si>
+  <si>
+    <t>HeroAtkJsonInfo</t>
+  </si>
+  <si>
+    <t>2_战斗技能.xlsx</t>
+  </si>
+  <si>
+    <t>战斗技能</t>
   </si>
 </sst>
 </file>
@@ -1066,8 +1078,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1183,6 +1195,23 @@
         <v>30</v>
       </c>
     </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
